--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/83.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/83.xlsx
@@ -426,13 +426,13 @@
         <v>-1.754348105964828</v>
       </c>
       <c r="E2">
-        <v>-12.32270112543493</v>
+        <v>-11.42852303362199</v>
       </c>
       <c r="F2">
-        <v>-3.678871731861823</v>
+        <v>-3.981843795966131</v>
       </c>
       <c r="G2">
-        <v>-11.48174087819621</v>
+        <v>-9.860622521045739</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.935324068863144</v>
       </c>
       <c r="E3">
-        <v>-14.08287361701051</v>
+        <v>-11.90703527641211</v>
       </c>
       <c r="F3">
-        <v>-4.092314872803473</v>
+        <v>-3.888881092554359</v>
       </c>
       <c r="G3">
-        <v>-10.77929524388357</v>
+        <v>-9.613677411661516</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.178343972122696</v>
       </c>
       <c r="E4">
-        <v>-13.40170958083671</v>
+        <v>-12.08654122308252</v>
       </c>
       <c r="F4">
-        <v>-3.832067514233355</v>
+        <v>-3.837212504172143</v>
       </c>
       <c r="G4">
-        <v>-9.833371569003699</v>
+        <v>-9.708892572271713</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.433896523948391</v>
       </c>
       <c r="E5">
-        <v>-13.94065935482573</v>
+        <v>-12.51403957116977</v>
       </c>
       <c r="F5">
-        <v>-3.81312855030315</v>
+        <v>-3.725044930893867</v>
       </c>
       <c r="G5">
-        <v>-9.797087440676407</v>
+        <v>-9.63908256727764</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.669271334344904</v>
       </c>
       <c r="E6">
-        <v>-15.97010530264657</v>
+        <v>-13.11167837438995</v>
       </c>
       <c r="F6">
-        <v>-3.597504515354438</v>
+        <v>-4.048920018040418</v>
       </c>
       <c r="G6">
-        <v>-9.614502406952308</v>
+        <v>-9.375349064800263</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.846915388083455</v>
       </c>
       <c r="E7">
-        <v>-14.05110985679822</v>
+        <v>-15.23762418734319</v>
       </c>
       <c r="F7">
-        <v>-3.333724169811381</v>
+        <v>-3.669058063240857</v>
       </c>
       <c r="G7">
-        <v>-10.24629607114024</v>
+        <v>-9.106860091050171</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.931986748900564</v>
       </c>
       <c r="E8">
-        <v>-16.78678862434953</v>
+        <v>-15.87642962121507</v>
       </c>
       <c r="F8">
-        <v>-3.688683743747983</v>
+        <v>-3.336457782240619</v>
       </c>
       <c r="G8">
-        <v>-10.17919601903175</v>
+        <v>-9.251651986073314</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.894392894052195</v>
       </c>
       <c r="E9">
-        <v>-17.99815577146227</v>
+        <v>-16.39486668447076</v>
       </c>
       <c r="F9">
-        <v>-3.479906993750812</v>
+        <v>-3.482307602484125</v>
       </c>
       <c r="G9">
-        <v>-9.687108519403465</v>
+        <v>-8.509525644720339</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.709356011665226</v>
       </c>
       <c r="E10">
-        <v>-18.6963189015886</v>
+        <v>-17.73260774577539</v>
       </c>
       <c r="F10">
-        <v>-3.32177248492379</v>
+        <v>-3.304235118639121</v>
       </c>
       <c r="G10">
-        <v>-8.517070696588656</v>
+        <v>-9.010671122707489</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.365133049216215</v>
       </c>
       <c r="E11">
-        <v>-20.2949563918963</v>
+        <v>-17.88622257304682</v>
       </c>
       <c r="F11">
-        <v>-3.323725775259591</v>
+        <v>-3.556555829531851</v>
       </c>
       <c r="G11">
-        <v>-7.920545581082068</v>
+        <v>-7.952273960097868</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.86801787525688</v>
       </c>
       <c r="E12">
-        <v>-19.86910686870501</v>
+        <v>-20.09722200072122</v>
       </c>
       <c r="F12">
-        <v>-3.483129342947703</v>
+        <v>-3.508998428569728</v>
       </c>
       <c r="G12">
-        <v>-8.555482581757706</v>
+        <v>-8.172918428471217</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.239993338512692</v>
       </c>
       <c r="E13">
-        <v>-20.95851496526416</v>
+        <v>-20.8235646696865</v>
       </c>
       <c r="F13">
-        <v>-3.123054600298814</v>
+        <v>-3.51008193313259</v>
       </c>
       <c r="G13">
-        <v>-7.998005067728104</v>
+        <v>-7.089174851998771</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.5259536506814487</v>
       </c>
       <c r="E14">
-        <v>-22.94459723364247</v>
+        <v>-21.56698534361949</v>
       </c>
       <c r="F14">
-        <v>-3.595426141540815</v>
+        <v>-3.521076853669948</v>
       </c>
       <c r="G14">
-        <v>-7.186662665775533</v>
+        <v>-6.789192466246082</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.227935364187826</v>
       </c>
       <c r="E15">
-        <v>-22.09960147033815</v>
+        <v>-22.09695172151291</v>
       </c>
       <c r="F15">
-        <v>-3.418018008352856</v>
+        <v>-3.311052582364161</v>
       </c>
       <c r="G15">
-        <v>-6.77078149538955</v>
+        <v>-6.185076610840832</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.9684112085927556</v>
       </c>
       <c r="E16">
-        <v>-24.01001638158941</v>
+        <v>-23.92412797139195</v>
       </c>
       <c r="F16">
-        <v>-2.760584219121028</v>
+        <v>-3.019979187633665</v>
       </c>
       <c r="G16">
-        <v>-7.026026161828923</v>
+        <v>-4.564822410150016</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.659752249619562</v>
       </c>
       <c r="E17">
-        <v>-24.05323054542425</v>
+        <v>-25.23790085014099</v>
       </c>
       <c r="F17">
-        <v>-2.977073898005665</v>
+        <v>-3.210142522089931</v>
       </c>
       <c r="G17">
-        <v>-4.985935512696589</v>
+        <v>-4.841026134166845</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.272500212446169</v>
       </c>
       <c r="E18">
-        <v>-23.99407635652472</v>
+        <v>-24.85273203187639</v>
       </c>
       <c r="F18">
-        <v>-2.948516760161555</v>
+        <v>-2.870702411444777</v>
       </c>
       <c r="G18">
-        <v>-4.524979836945035</v>
+        <v>-4.532013182873495</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.789315254465545</v>
       </c>
       <c r="E19">
-        <v>-26.13433828891463</v>
+        <v>-25.62473510614685</v>
       </c>
       <c r="F19">
-        <v>-3.042599416301912</v>
+        <v>-2.767243464672133</v>
       </c>
       <c r="G19">
-        <v>-4.068932361024776</v>
+        <v>-3.965982869563406</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.201721810302685</v>
       </c>
       <c r="E20">
-        <v>-28.34764274887431</v>
+        <v>-27.17321841649592</v>
       </c>
       <c r="F20">
-        <v>-2.886801731918186</v>
+        <v>-2.457959240958493</v>
       </c>
       <c r="G20">
-        <v>-5.054402289598534</v>
+        <v>-4.126462728834548</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.502287124364146</v>
       </c>
       <c r="E21">
-        <v>-27.32333623983185</v>
+        <v>-28.36531050985013</v>
       </c>
       <c r="F21">
-        <v>-2.52188103996292</v>
+        <v>-2.562666537407156</v>
       </c>
       <c r="G21">
-        <v>-4.321349591071972</v>
+        <v>-3.246829775239931</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.693967196153533</v>
       </c>
       <c r="E22">
-        <v>-28.79731924543615</v>
+        <v>-28.86949790505034</v>
       </c>
       <c r="F22">
-        <v>-2.193398573321999</v>
+        <v>-2.318028105807989</v>
       </c>
       <c r="G22">
-        <v>-3.964079636756484</v>
+        <v>-3.73889508353919</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.777921827833497</v>
       </c>
       <c r="E23">
-        <v>-28.94315303129051</v>
+        <v>-29.50207352193498</v>
       </c>
       <c r="F23">
-        <v>-2.607738007793477</v>
+        <v>-2.67358493264201</v>
       </c>
       <c r="G23">
-        <v>-4.57991251388665</v>
+        <v>-2.93786381734922</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.762180157159758</v>
       </c>
       <c r="E24">
-        <v>-29.48364987649804</v>
+        <v>-29.99982759279303</v>
       </c>
       <c r="F24">
-        <v>-2.17105004916187</v>
+        <v>-2.163466345589241</v>
       </c>
       <c r="G24">
-        <v>-3.90180815676925</v>
+        <v>-2.897848935001227</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.654494449275134</v>
       </c>
       <c r="E25">
-        <v>-30.32206487645816</v>
+        <v>-30.2442876879781</v>
       </c>
       <c r="F25">
-        <v>-1.822255185436902</v>
+        <v>-2.024595520714321</v>
       </c>
       <c r="G25">
-        <v>-3.959657035419138</v>
+        <v>-3.09566505266988</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.46426980109833</v>
       </c>
       <c r="E26">
-        <v>-30.72115525908359</v>
+        <v>-31.11122279010582</v>
       </c>
       <c r="F26">
-        <v>-2.332962741713062</v>
+        <v>-1.681464204922293</v>
       </c>
       <c r="G26">
-        <v>-4.316530156556778</v>
+        <v>-2.28632900793558</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.20135657436678</v>
       </c>
       <c r="E27">
-        <v>-28.29766715700265</v>
+        <v>-31.54120683517099</v>
       </c>
       <c r="F27">
-        <v>-2.338613035767557</v>
+        <v>-1.756347789767965</v>
       </c>
       <c r="G27">
-        <v>-4.9362243249372</v>
+        <v>-2.788766804495332</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.876865594346589</v>
       </c>
       <c r="E28">
-        <v>-29.36262322188687</v>
+        <v>-30.58484894000838</v>
       </c>
       <c r="F28">
-        <v>-1.314146217703325</v>
+        <v>-1.990764995983989</v>
       </c>
       <c r="G28">
-        <v>-3.959166215436009</v>
+        <v>-3.337819445729411</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.499362925136491</v>
       </c>
       <c r="E29">
-        <v>-29.90788380048398</v>
+        <v>-30.58455198539865</v>
       </c>
       <c r="F29">
-        <v>-2.173624615049771</v>
+        <v>-2.32075923313502</v>
       </c>
       <c r="G29">
-        <v>-3.609566628729211</v>
+        <v>-3.345030322290066</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.082633850223479</v>
       </c>
       <c r="E30">
-        <v>-29.22363808150715</v>
+        <v>-31.71007640763851</v>
       </c>
       <c r="F30">
-        <v>-1.993660968424176</v>
+        <v>-2.289089090591189</v>
       </c>
       <c r="G30">
-        <v>-4.445866443600529</v>
+        <v>-3.150558568442628</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.634657088609117</v>
       </c>
       <c r="E31">
-        <v>-30.36402477047291</v>
+        <v>-31.35598191650628</v>
       </c>
       <c r="F31">
-        <v>-1.691699512551283</v>
+        <v>-2.180878628396087</v>
       </c>
       <c r="G31">
-        <v>-4.982964485351902</v>
+        <v>-3.731253434121001</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.170995863042464</v>
       </c>
       <c r="E32">
-        <v>-29.09695682967723</v>
+        <v>-31.11509981287755</v>
       </c>
       <c r="F32">
-        <v>-2.156066539580033</v>
+        <v>-2.091868894230474</v>
       </c>
       <c r="G32">
-        <v>-5.302175005018141</v>
+        <v>-3.438834375448766</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.7016066101888937</v>
       </c>
       <c r="E33">
-        <v>-28.21346079739175</v>
+        <v>-30.04419634937617</v>
       </c>
       <c r="F33">
-        <v>-2.148289826402551</v>
+        <v>-1.779390485811639</v>
       </c>
       <c r="G33">
-        <v>-4.05217399149442</v>
+        <v>-3.904674754330292</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.2397163345459533</v>
       </c>
       <c r="E34">
-        <v>-27.94738946707794</v>
+        <v>-30.11436693131481</v>
       </c>
       <c r="F34">
-        <v>-1.988626979717363</v>
+        <v>-1.99698520681161</v>
       </c>
       <c r="G34">
-        <v>-5.53961439334612</v>
+        <v>-4.324534699473131</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.2027565598669388</v>
       </c>
       <c r="E35">
-        <v>-29.51837279977927</v>
+        <v>-28.87191715064706</v>
       </c>
       <c r="F35">
-        <v>-2.251118385581665</v>
+        <v>-1.763587720868433</v>
       </c>
       <c r="G35">
-        <v>-6.64942103307165</v>
+        <v>-4.282634859530353</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.6205120595520188</v>
       </c>
       <c r="E36">
-        <v>-27.05885974266677</v>
+        <v>-28.090604653192</v>
       </c>
       <c r="F36">
-        <v>-2.1848771578494</v>
+        <v>-1.889783696113118</v>
       </c>
       <c r="G36">
-        <v>-4.96598159178671</v>
+        <v>-4.854938792092888</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.003831544978513</v>
       </c>
       <c r="E37">
-        <v>-26.67176798755877</v>
+        <v>-28.5635931249201</v>
       </c>
       <c r="F37">
-        <v>-1.643347707249876</v>
+        <v>-1.288371565965218</v>
       </c>
       <c r="G37">
-        <v>-5.776529022011287</v>
+        <v>-5.030574023715443</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.355796877456306</v>
       </c>
       <c r="E38">
-        <v>-26.24401629358071</v>
+        <v>-27.37276360780863</v>
       </c>
       <c r="F38">
-        <v>-2.079088841940083</v>
+        <v>-1.16751856046859</v>
       </c>
       <c r="G38">
-        <v>-6.472133200122919</v>
+        <v>-5.301496211424451</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.672565244460372</v>
       </c>
       <c r="E39">
-        <v>-26.42807000665181</v>
+        <v>-26.20353909600893</v>
       </c>
       <c r="F39">
-        <v>-1.423103038928349</v>
+        <v>-1.585325540888188</v>
       </c>
       <c r="G39">
-        <v>-5.703637033027404</v>
+        <v>-5.424368294860606</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.962407284756725</v>
       </c>
       <c r="E40">
-        <v>-24.69588185298292</v>
+        <v>-25.90668416335548</v>
       </c>
       <c r="F40">
-        <v>-2.427159712555005</v>
+        <v>-1.591302211699386</v>
       </c>
       <c r="G40">
-        <v>-6.476936970170568</v>
+        <v>-5.997220483787275</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.227915033164374</v>
       </c>
       <c r="E41">
-        <v>-23.14826656380074</v>
+        <v>-25.03156100510086</v>
       </c>
       <c r="F41">
-        <v>-1.776241032946195</v>
+        <v>-1.263364810809507</v>
       </c>
       <c r="G41">
-        <v>-7.882493978666592</v>
+        <v>-6.030363886371458</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.477321777754692</v>
       </c>
       <c r="E42">
-        <v>-24.62482456042643</v>
+        <v>-23.83297744244594</v>
       </c>
       <c r="F42">
-        <v>-1.34170765792927</v>
+        <v>-1.406512496585081</v>
       </c>
       <c r="G42">
-        <v>-6.972414521650411</v>
+        <v>-6.764171090084852</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.719099765449102</v>
       </c>
       <c r="E43">
-        <v>-23.33045133177566</v>
+        <v>-22.72669900148534</v>
       </c>
       <c r="F43">
-        <v>-1.38560698844063</v>
+        <v>-1.569260183478294</v>
       </c>
       <c r="G43">
-        <v>-8.066650680634542</v>
+        <v>-6.272275480184016</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.960205334459808</v>
       </c>
       <c r="E44">
-        <v>-23.43737575733337</v>
+        <v>-23.66802850146905</v>
       </c>
       <c r="F44">
-        <v>-1.395172146840755</v>
+        <v>-1.430823423122441</v>
       </c>
       <c r="G44">
-        <v>-7.52976410919505</v>
+        <v>-6.913581392289674</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.213813820972354</v>
       </c>
       <c r="E45">
-        <v>-21.88386290806993</v>
+        <v>-22.67554805080875</v>
       </c>
       <c r="F45">
-        <v>-1.781685063517394</v>
+        <v>-1.187773800201843</v>
       </c>
       <c r="G45">
-        <v>-6.755409431237076</v>
+        <v>-7.543410471172798</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.484218893946724</v>
       </c>
       <c r="E46">
-        <v>-21.63017645392676</v>
+        <v>-21.58947913615476</v>
       </c>
       <c r="F46">
-        <v>-1.616346243388223</v>
+        <v>-0.8491670271639061</v>
       </c>
       <c r="G46">
-        <v>-7.137405747574999</v>
+        <v>-7.924075307769254</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.784921079527349</v>
       </c>
       <c r="E47">
-        <v>-21.38485456739178</v>
+        <v>-20.45686518218342</v>
       </c>
       <c r="F47">
-        <v>-1.525313636024975</v>
+        <v>-0.9221660761682098</v>
       </c>
       <c r="G47">
-        <v>-9.016618398886045</v>
+        <v>-7.902724638503129</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.115996914477204</v>
       </c>
       <c r="E48">
-        <v>-20.17228714220617</v>
+        <v>-18.89436063040172</v>
       </c>
       <c r="F48">
-        <v>-1.144483319731541</v>
+        <v>-0.5857428796040521</v>
       </c>
       <c r="G48">
-        <v>-7.731167389931893</v>
+        <v>-8.692853435280609</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.484968956441781</v>
       </c>
       <c r="E49">
-        <v>-20.93913192801119</v>
+        <v>-18.38578329083117</v>
       </c>
       <c r="F49">
-        <v>-1.682753972968452</v>
+        <v>-1.134799704792815</v>
       </c>
       <c r="G49">
-        <v>-8.211531340973782</v>
+        <v>-9.128166377658248</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.889459785661286</v>
       </c>
       <c r="E50">
-        <v>-18.32672462579211</v>
+        <v>-18.51812952290816</v>
       </c>
       <c r="F50">
-        <v>-1.454604194522009</v>
+        <v>-0.872068900749104</v>
       </c>
       <c r="G50">
-        <v>-8.427361596321116</v>
+        <v>-8.615678519795004</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.326941531232263</v>
       </c>
       <c r="E51">
-        <v>-17.95015710818123</v>
+        <v>-16.26474657366388</v>
       </c>
       <c r="F51">
-        <v>-1.718882388874149</v>
+        <v>-1.223184849936717</v>
       </c>
       <c r="G51">
-        <v>-8.18266172728525</v>
+        <v>-9.335590035422198</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.792972191810089</v>
       </c>
       <c r="E52">
-        <v>-16.62416548171455</v>
+        <v>-15.58798078828307</v>
       </c>
       <c r="F52">
-        <v>-1.23936866388521</v>
+        <v>-0.885365025931439</v>
       </c>
       <c r="G52">
-        <v>-8.619144283239708</v>
+        <v>-9.429971063135534</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.27642620851918</v>
       </c>
       <c r="E53">
-        <v>-17.26949145736641</v>
+        <v>-15.49272273333681</v>
       </c>
       <c r="F53">
-        <v>-2.665427998826643</v>
+        <v>-1.104831028894334</v>
       </c>
       <c r="G53">
-        <v>-8.0474786777297</v>
+        <v>-9.472061487433463</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.773388343857231</v>
       </c>
       <c r="E54">
-        <v>-15.4249589373609</v>
+        <v>-14.23339845505627</v>
       </c>
       <c r="F54">
-        <v>-1.831275278085986</v>
+        <v>-1.002123411356029</v>
       </c>
       <c r="G54">
-        <v>-9.411134540910652</v>
+        <v>-9.333467500069624</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.266969309462347</v>
       </c>
       <c r="E55">
-        <v>-16.1783016331489</v>
+        <v>-14.4893193368922</v>
       </c>
       <c r="F55">
-        <v>-1.006040760803868</v>
+        <v>-1.488871268873616</v>
       </c>
       <c r="G55">
-        <v>-9.928330876643967</v>
+        <v>-9.450907929383968</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.754381823668548</v>
       </c>
       <c r="E56">
-        <v>-14.61183491776332</v>
+        <v>-13.01742539658429</v>
       </c>
       <c r="F56">
-        <v>-1.344425531377855</v>
+        <v>-1.303417203102265</v>
       </c>
       <c r="G56">
-        <v>-9.535505191742107</v>
+        <v>-9.757260531938973</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.220896887744948</v>
       </c>
       <c r="E57">
-        <v>-16.47904397160239</v>
+        <v>-12.29347913055343</v>
       </c>
       <c r="F57">
-        <v>-2.181496590478575</v>
+        <v>-1.180472569913569</v>
       </c>
       <c r="G57">
-        <v>-9.698791601448695</v>
+        <v>-10.08443382260811</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.658686726388755</v>
       </c>
       <c r="E58">
-        <v>-14.11526451213285</v>
+        <v>-11.69451960613196</v>
       </c>
       <c r="F58">
-        <v>-2.07766156490506</v>
+        <v>-1.180129625808809</v>
       </c>
       <c r="G58">
-        <v>-10.05912134842497</v>
+        <v>-11.17866606547535</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.056025062921201</v>
       </c>
       <c r="E59">
-        <v>-13.12456163591957</v>
+        <v>-10.60239946257769</v>
       </c>
       <c r="F59">
-        <v>-2.480848689032649</v>
+        <v>-1.54491860734703</v>
       </c>
       <c r="G59">
-        <v>-9.309697975939832</v>
+        <v>-10.46911790050258</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.40259637974931</v>
       </c>
       <c r="E60">
-        <v>-13.06620071038308</v>
+        <v>-11.19344296621404</v>
       </c>
       <c r="F60">
-        <v>-2.315666430342608</v>
+        <v>-1.521959576411039</v>
       </c>
       <c r="G60">
-        <v>-9.538403118238243</v>
+        <v>-10.46557642546474</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.692379729510742</v>
       </c>
       <c r="E61">
-        <v>-13.83654665333493</v>
+        <v>-9.748540746306194</v>
       </c>
       <c r="F61">
-        <v>-2.140467553017916</v>
+        <v>-1.425309809689407</v>
       </c>
       <c r="G61">
-        <v>-9.908333878448335</v>
+        <v>-10.53582764629471</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.916227449816212</v>
       </c>
       <c r="E62">
-        <v>-11.63766214309505</v>
+        <v>-9.008480020334996</v>
       </c>
       <c r="F62">
-        <v>-2.532803064168831</v>
+        <v>-1.657313981661076</v>
       </c>
       <c r="G62">
-        <v>-9.468646633508287</v>
+        <v>-10.53034116653648</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.07596534631286</v>
       </c>
       <c r="E63">
-        <v>-11.24832765387165</v>
+        <v>-9.30043001041382</v>
       </c>
       <c r="F63">
-        <v>-2.198004296081563</v>
+        <v>-1.493620299193866</v>
       </c>
       <c r="G63">
-        <v>-9.647532242146777</v>
+        <v>-10.72717433886658</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.16750106759605</v>
       </c>
       <c r="E64">
-        <v>-12.99560442428364</v>
+        <v>-8.166927269218963</v>
       </c>
       <c r="F64">
-        <v>-2.704289198794176</v>
+        <v>-1.948038633714993</v>
       </c>
       <c r="G64">
-        <v>-11.07116865693626</v>
+        <v>-10.73512144540193</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.19704823194659</v>
       </c>
       <c r="E65">
-        <v>-10.05103573993876</v>
+        <v>-8.452460547800927</v>
       </c>
       <c r="F65">
-        <v>-2.272994740322197</v>
+        <v>-2.205775210687225</v>
       </c>
       <c r="G65">
-        <v>-10.35636506310158</v>
+        <v>-10.72362111547808</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.1657082867473</v>
       </c>
       <c r="E66">
-        <v>-10.70089702235733</v>
+        <v>-7.833137828253819</v>
       </c>
       <c r="F66">
-        <v>-2.155539697911852</v>
+        <v>-1.732057572415675</v>
       </c>
       <c r="G66">
-        <v>-10.95272570169893</v>
+        <v>-10.22239209366401</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.08178174541782</v>
       </c>
       <c r="E67">
-        <v>-9.826135193487966</v>
+        <v>-6.768279363835729</v>
       </c>
       <c r="F67">
-        <v>-2.396323735985793</v>
+        <v>-2.207750866942903</v>
       </c>
       <c r="G67">
-        <v>-9.865047733127676</v>
+        <v>-10.71006351881643</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.948761378195265</v>
       </c>
       <c r="E68">
-        <v>-11.47060752397648</v>
+        <v>-7.217665135604827</v>
       </c>
       <c r="F68">
-        <v>-2.387889299090489</v>
+        <v>-1.914440880224848</v>
       </c>
       <c r="G68">
-        <v>-10.56735760872158</v>
+        <v>-10.24826196181735</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.77572244292883</v>
       </c>
       <c r="E69">
-        <v>-10.07348384714945</v>
+        <v>-7.95714441199055</v>
       </c>
       <c r="F69">
-        <v>-2.892934135801111</v>
+        <v>-2.325108161999717</v>
       </c>
       <c r="G69">
-        <v>-9.833299773527443</v>
+        <v>-10.03800434079975</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.570078063144948</v>
       </c>
       <c r="E70">
-        <v>-11.31295577529731</v>
+        <v>-6.916046469561804</v>
       </c>
       <c r="F70">
-        <v>-2.071404077544312</v>
+        <v>-2.334761955711942</v>
       </c>
       <c r="G70">
-        <v>-10.12173091983675</v>
+        <v>-9.436903895397236</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.337599939049877</v>
       </c>
       <c r="E71">
-        <v>-9.664807852786327</v>
+        <v>-7.005029022196256</v>
       </c>
       <c r="F71">
-        <v>-2.730522766073434</v>
+        <v>-2.529205464538473</v>
       </c>
       <c r="G71">
-        <v>-10.25441026532943</v>
+        <v>-9.583985413426785</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.088718480875755</v>
       </c>
       <c r="E72">
-        <v>-9.537852489008968</v>
+        <v>-7.717026499245587</v>
       </c>
       <c r="F72">
-        <v>-2.182378801762556</v>
+        <v>-2.142387708657605</v>
       </c>
       <c r="G72">
-        <v>-9.798788340777516</v>
+        <v>-8.959022762461496</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.827327949852439</v>
       </c>
       <c r="E73">
-        <v>-11.33081043078275</v>
+        <v>-7.301987785132821</v>
       </c>
       <c r="F73">
-        <v>-3.150746922574401</v>
+        <v>-2.148558217441058</v>
       </c>
       <c r="G73">
-        <v>-9.634821832104944</v>
+        <v>-9.314069667757652</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.564334464749974</v>
       </c>
       <c r="E74">
-        <v>-11.61737370577327</v>
+        <v>-7.219509161433051</v>
       </c>
       <c r="F74">
-        <v>-2.398407080003834</v>
+        <v>-2.145151970680747</v>
       </c>
       <c r="G74">
-        <v>-9.201790680499938</v>
+        <v>-8.44627121939455</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.300115802907138</v>
       </c>
       <c r="E75">
-        <v>-11.05235007108697</v>
+        <v>-7.761561384281723</v>
       </c>
       <c r="F75">
-        <v>-3.4592201746007</v>
+        <v>-2.498976681275514</v>
       </c>
       <c r="G75">
-        <v>-8.56652472600582</v>
+        <v>-8.623722223880225</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.045768296847713</v>
       </c>
       <c r="E76">
-        <v>-11.5269499888091</v>
+        <v>-7.602850566714726</v>
       </c>
       <c r="F76">
-        <v>-2.456676099851557</v>
+        <v>-2.408503221909154</v>
       </c>
       <c r="G76">
-        <v>-8.199080700018763</v>
+        <v>-8.132201255828214</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.802704124713674</v>
       </c>
       <c r="E77">
-        <v>-11.49219591644294</v>
+        <v>-8.993079912742532</v>
       </c>
       <c r="F77">
-        <v>-2.902284747043911</v>
+        <v>-2.750388673127372</v>
       </c>
       <c r="G77">
-        <v>-8.309464286703328</v>
+        <v>-7.876132899470345</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.57507833509661</v>
       </c>
       <c r="E78">
-        <v>-9.267220932660489</v>
+        <v>-8.949944659922863</v>
       </c>
       <c r="F78">
-        <v>-3.49365375080027</v>
+        <v>-2.637975903097868</v>
       </c>
       <c r="G78">
-        <v>-8.92267206014713</v>
+        <v>-7.456665871388468</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.365852927171697</v>
       </c>
       <c r="E79">
-        <v>-13.15014541768051</v>
+        <v>-9.180742766454911</v>
       </c>
       <c r="F79">
-        <v>-3.359329834599317</v>
+        <v>-2.654151433372334</v>
       </c>
       <c r="G79">
-        <v>-7.789208158309227</v>
+        <v>-7.375745842786912</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.173935669947757</v>
       </c>
       <c r="E80">
-        <v>-13.59876284535452</v>
+        <v>-9.173993798052063</v>
       </c>
       <c r="F80">
-        <v>-2.759677985182365</v>
+        <v>-2.759530535784667</v>
       </c>
       <c r="G80">
-        <v>-7.632902879639276</v>
+        <v>-6.199555800343146</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.001826321745032</v>
       </c>
       <c r="E81">
-        <v>-14.28756463715468</v>
+        <v>-9.376155512499418</v>
       </c>
       <c r="F81">
-        <v>-2.638239323931958</v>
+        <v>-2.57832350968747</v>
       </c>
       <c r="G81">
-        <v>-6.370136630437305</v>
+        <v>-6.450367422466808</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.843755921629407</v>
       </c>
       <c r="E82">
-        <v>-14.74054293671976</v>
+        <v>-10.26710655911296</v>
       </c>
       <c r="F82">
-        <v>-3.441320811761009</v>
+        <v>-2.718189203813152</v>
       </c>
       <c r="G82">
-        <v>-7.249325757451434</v>
+        <v>-6.478827149254534</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.701911995287694</v>
       </c>
       <c r="E83">
-        <v>-14.56463367105665</v>
+        <v>-11.22297229873358</v>
       </c>
       <c r="F83">
-        <v>-2.869655355047639</v>
+        <v>-2.358046535037233</v>
       </c>
       <c r="G83">
-        <v>-7.836238111373542</v>
+        <v>-5.66017335707455</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.56994840148873</v>
       </c>
       <c r="E84">
-        <v>-15.11201446403507</v>
+        <v>-12.79867160289425</v>
       </c>
       <c r="F84">
-        <v>-3.023695243802624</v>
+        <v>-2.919634902295547</v>
       </c>
       <c r="G84">
-        <v>-7.022911543531725</v>
+        <v>-5.576867107916716</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.447759353105962</v>
       </c>
       <c r="E85">
-        <v>-17.61378852298337</v>
+        <v>-13.7529715818454</v>
       </c>
       <c r="F85">
-        <v>-3.113549912719092</v>
+        <v>-2.372864371138511</v>
       </c>
       <c r="G85">
-        <v>-7.240728575512898</v>
+        <v>-5.24333665416822</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.333531903741929</v>
       </c>
       <c r="E86">
-        <v>-18.148859197595</v>
+        <v>-15.04545094613205</v>
       </c>
       <c r="F86">
-        <v>-3.412898697803555</v>
+        <v>-2.905078830293554</v>
       </c>
       <c r="G86">
-        <v>-7.039168650100588</v>
+        <v>-5.325005966467426</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.224868451162952</v>
       </c>
       <c r="E87">
-        <v>-18.73928802595528</v>
+        <v>-15.59347548686582</v>
       </c>
       <c r="F87">
-        <v>-2.569450866436084</v>
+        <v>-2.755696023077108</v>
       </c>
       <c r="G87">
-        <v>-6.75195019465385</v>
+        <v>-5.028725616544935</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.125396724601286</v>
       </c>
       <c r="E88">
-        <v>-20.5324536282953</v>
+        <v>-16.77350665453273</v>
       </c>
       <c r="F88">
-        <v>-3.489727289311001</v>
+        <v>-3.014278363167599</v>
       </c>
       <c r="G88">
-        <v>-6.765131844094381</v>
+        <v>-5.946961039663753</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.035169005863168</v>
       </c>
       <c r="E89">
-        <v>-20.58104204758447</v>
+        <v>-19.58071202752024</v>
       </c>
       <c r="F89">
-        <v>-3.140113998592066</v>
+        <v>-3.205708271382745</v>
       </c>
       <c r="G89">
-        <v>-5.420822903705875</v>
+        <v>-5.178036710455295</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.961987200213829</v>
       </c>
       <c r="E90">
-        <v>-23.1054220357738</v>
+        <v>-19.84149216660622</v>
       </c>
       <c r="F90">
-        <v>-3.201976476233134</v>
+        <v>-2.864464804901697</v>
       </c>
       <c r="G90">
-        <v>-5.640368248606364</v>
+        <v>-4.468820110045598</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.907771042577541</v>
       </c>
       <c r="E91">
-        <v>-25.33313398581931</v>
+        <v>-22.03462863237253</v>
       </c>
       <c r="F91">
-        <v>-2.958216942448337</v>
+        <v>-3.183677840305292</v>
       </c>
       <c r="G91">
-        <v>-5.506656353627906</v>
+        <v>-5.19594119686115</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.879256201854667</v>
       </c>
       <c r="E92">
-        <v>-26.09246976554904</v>
+        <v>-21.8143713761829</v>
       </c>
       <c r="F92">
-        <v>-3.638801943853605</v>
+        <v>-3.2039786402457</v>
       </c>
       <c r="G92">
-        <v>-6.611074416517377</v>
+        <v>-5.122725475547969</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.878561260797895</v>
       </c>
       <c r="E93">
-        <v>-27.16351651484112</v>
+        <v>-24.244452701242</v>
       </c>
       <c r="F93">
-        <v>-3.105632377083134</v>
+        <v>-2.88514002690817</v>
       </c>
       <c r="G93">
-        <v>-5.80460758008871</v>
+        <v>-5.635906486100152</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.903008455147021</v>
       </c>
       <c r="E94">
-        <v>-29.14836112624463</v>
+        <v>-26.66951279380939</v>
       </c>
       <c r="F94">
-        <v>-2.719063131423106</v>
+        <v>-2.887456970533801</v>
       </c>
       <c r="G94">
-        <v>-6.814558460693338</v>
+        <v>-5.257747964311166</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.952630863845306</v>
       </c>
       <c r="E95">
-        <v>-30.51574780998588</v>
+        <v>-27.91163031757116</v>
       </c>
       <c r="F95">
-        <v>-3.271189057839241</v>
+        <v>-3.072670809758339</v>
       </c>
       <c r="G95">
-        <v>-7.203295719565515</v>
+        <v>-5.821606138121449</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.016525426317012</v>
       </c>
       <c r="E96">
-        <v>-32.79470623456844</v>
+        <v>-30.17789445173939</v>
       </c>
       <c r="F96">
-        <v>-2.904059110020708</v>
+        <v>-3.176283004500501</v>
       </c>
       <c r="G96">
-        <v>-7.649813977728211</v>
+        <v>-5.387904025156527</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.089329342097098</v>
       </c>
       <c r="E97">
-        <v>-33.63551140764601</v>
+        <v>-31.59148353486369</v>
       </c>
       <c r="F97">
-        <v>-3.06740404981134</v>
+        <v>-2.874657037425743</v>
       </c>
       <c r="G97">
-        <v>-8.523138067018403</v>
+        <v>-6.67421005296427</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.150972620738678</v>
       </c>
       <c r="E98">
-        <v>-36.29335484175871</v>
+        <v>-33.79848134342662</v>
       </c>
       <c r="F98">
-        <v>-2.976447652249149</v>
+        <v>-2.821890862234817</v>
       </c>
       <c r="G98">
-        <v>-8.187768343705468</v>
+        <v>-6.508537422701403</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.195594699557642</v>
       </c>
       <c r="E99">
-        <v>-39.91237597277648</v>
+        <v>-36.7757254178696</v>
       </c>
       <c r="F99">
-        <v>-2.910813617823135</v>
+        <v>-2.607211166125297</v>
       </c>
       <c r="G99">
-        <v>-8.4451107434238</v>
+        <v>-6.850714662535666</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.198236933853166</v>
       </c>
       <c r="E100">
-        <v>-40.40641499610447</v>
+        <v>-38.90083228213522</v>
       </c>
       <c r="F100">
-        <v>-3.056383449884495</v>
+        <v>-3.035616279096311</v>
       </c>
       <c r="G100">
-        <v>-7.493286785768015</v>
+        <v>-7.369493109491196</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.163440131530024</v>
       </c>
       <c r="E101">
-        <v>-43.83621997237438</v>
+        <v>-40.49179463791464</v>
       </c>
       <c r="F101">
-        <v>-3.325729596006963</v>
+        <v>-3.3196154162069</v>
       </c>
       <c r="G101">
-        <v>-8.718078449519945</v>
+        <v>-7.78188371435886</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.060675096791973</v>
       </c>
       <c r="E102">
-        <v>-45.05733262986083</v>
+        <v>-42.84401778687284</v>
       </c>
       <c r="F102">
-        <v>-3.30291801446867</v>
+        <v>-2.307877291654084</v>
       </c>
       <c r="G102">
-        <v>-8.662668006318157</v>
+        <v>-7.520556013022193</v>
       </c>
     </row>
   </sheetData>
